--- a/لجان مناقشة مذكرات كل التخصصات 2023-2024 حذف المواضيع الزائدة بعد اختماع 22-05-2024 (2).xlsx
+++ b/لجان مناقشة مذكرات كل التخصصات 2023-2024 حذف المواضيع الزائدة بعد اختماع 22-05-2024 (2).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\1الجامعة\مشاريع Github\master-tiaret2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D06FA66E-4858-444B-8F3C-65F2B1A2DC12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCD1D856-468D-4EDA-A645-1740502A2127}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="13920" tabRatio="702" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2600,44 +2600,17 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2665,6 +2638,33 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -10434,7 +10434,7 @@
         <v>1</v>
       </c>
       <c r="H72" s="49">
-        <f t="shared" ref="H72:H103" si="8">SUM(D72:G72)</f>
+        <f t="shared" ref="H72:H84" si="8">SUM(D72:G72)</f>
         <v>1</v>
       </c>
       <c r="I72" s="22"/>
@@ -10442,7 +10442,7 @@
       <c r="K72" s="22"/>
       <c r="L72" s="22"/>
       <c r="M72" s="49">
-        <f t="shared" ref="M72:M103" si="9">SUM(I72:L72)</f>
+        <f t="shared" ref="M72:M84" si="9">SUM(I72:L72)</f>
         <v>0</v>
       </c>
       <c r="N72" s="22"/>
@@ -10450,11 +10450,11 @@
       <c r="P72" s="22"/>
       <c r="Q72" s="22"/>
       <c r="R72" s="49">
-        <f t="shared" ref="R72:R103" si="10">SUM(N72:Q72)</f>
+        <f t="shared" ref="R72:R84" si="10">SUM(N72:Q72)</f>
         <v>0</v>
       </c>
       <c r="S72" s="39">
-        <f t="shared" ref="S72:S103" si="11">SUM(R72,M72,H72)</f>
+        <f t="shared" ref="S72:S84" si="11">SUM(R72,M72,H72)</f>
         <v>1</v>
       </c>
       <c r="T72">
@@ -11539,79 +11539,79 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="23.25">
-      <c r="A1" s="103" t="s">
+      <c r="A1" s="93" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="103"/>
-      <c r="C1" s="103"/>
-      <c r="D1" s="103"/>
-      <c r="E1" s="103"/>
-      <c r="F1" s="103"/>
-      <c r="G1" s="103"/>
-      <c r="H1" s="103"/>
+      <c r="B1" s="93"/>
+      <c r="C1" s="93"/>
+      <c r="D1" s="93"/>
+      <c r="E1" s="93"/>
+      <c r="F1" s="93"/>
+      <c r="G1" s="93"/>
+      <c r="H1" s="93"/>
     </row>
     <row r="2" spans="1:9" ht="23.25">
-      <c r="A2" s="103" t="s">
+      <c r="A2" s="93" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="103"/>
-      <c r="C2" s="103"/>
-      <c r="D2" s="103"/>
-      <c r="E2" s="103"/>
-      <c r="F2" s="103"/>
-      <c r="G2" s="103"/>
-      <c r="H2" s="103"/>
+      <c r="B2" s="93"/>
+      <c r="C2" s="93"/>
+      <c r="D2" s="93"/>
+      <c r="E2" s="93"/>
+      <c r="F2" s="93"/>
+      <c r="G2" s="93"/>
+      <c r="H2" s="93"/>
     </row>
     <row r="3" spans="1:9" ht="23.25">
-      <c r="A3" s="103" t="s">
+      <c r="A3" s="93" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="103"/>
-      <c r="C3" s="103"/>
-      <c r="D3" s="103"/>
-      <c r="E3" s="103"/>
-      <c r="F3" s="103"/>
-      <c r="G3" s="103"/>
-      <c r="H3" s="103"/>
+      <c r="B3" s="93"/>
+      <c r="C3" s="93"/>
+      <c r="D3" s="93"/>
+      <c r="E3" s="93"/>
+      <c r="F3" s="93"/>
+      <c r="G3" s="93"/>
+      <c r="H3" s="93"/>
     </row>
     <row r="4" spans="1:9" ht="23.25">
-      <c r="A4" s="103" t="s">
+      <c r="A4" s="93" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="103"/>
-      <c r="C4" s="103"/>
-      <c r="D4" s="103"/>
-      <c r="E4" s="103"/>
-      <c r="F4" s="103"/>
-      <c r="G4" s="103"/>
-      <c r="H4" s="103"/>
+      <c r="B4" s="93"/>
+      <c r="C4" s="93"/>
+      <c r="D4" s="93"/>
+      <c r="E4" s="93"/>
+      <c r="F4" s="93"/>
+      <c r="G4" s="93"/>
+      <c r="H4" s="93"/>
     </row>
     <row r="5" spans="1:9" ht="27" thickBot="1">
-      <c r="A5" s="104" t="s">
+      <c r="A5" s="107" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="104"/>
-      <c r="C5" s="104"/>
-      <c r="E5" s="93" t="s">
+      <c r="B5" s="107"/>
+      <c r="C5" s="107"/>
+      <c r="E5" s="96" t="s">
         <v>195</v>
       </c>
-      <c r="F5" s="93"/>
-      <c r="G5" s="93"/>
-      <c r="H5" s="93"/>
+      <c r="F5" s="96"/>
+      <c r="G5" s="96"/>
+      <c r="H5" s="96"/>
     </row>
     <row r="6" spans="1:9" ht="21.75" thickTop="1">
-      <c r="C6" s="109" t="s">
+      <c r="C6" s="100" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="110"/>
-      <c r="E6" s="110"/>
-      <c r="F6" s="111"/>
+      <c r="D6" s="101"/>
+      <c r="E6" s="101"/>
+      <c r="F6" s="102"/>
     </row>
     <row r="7" spans="1:9" ht="21.75" thickBot="1">
-      <c r="C7" s="112"/>
-      <c r="D7" s="113"/>
-      <c r="E7" s="113"/>
-      <c r="F7" s="114"/>
+      <c r="C7" s="103"/>
+      <c r="D7" s="104"/>
+      <c r="E7" s="104"/>
+      <c r="F7" s="105"/>
     </row>
     <row r="8" spans="1:9" ht="30.75" thickTop="1">
       <c r="A8" s="3" t="s">
@@ -11620,25 +11620,25 @@
       <c r="B8" s="24">
         <v>12007</v>
       </c>
-      <c r="C8" s="102" t="s">
+      <c r="C8" s="106" t="s">
         <v>196</v>
       </c>
-      <c r="D8" s="102"/>
+      <c r="D8" s="106"/>
     </row>
     <row r="9" spans="1:9" ht="26.25">
-      <c r="A9" s="93" t="s">
+      <c r="A9" s="96" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="93"/>
-      <c r="C9" s="93" t="str">
+      <c r="B9" s="96"/>
+      <c r="C9" s="96" t="str">
         <f>VLOOKUP(B8,'كل التخصصات'!A3:O87,5,1)</f>
         <v>ميساوي فتيحة</v>
       </c>
-      <c r="D9" s="93"/>
-      <c r="E9" s="94" t="s">
+      <c r="D9" s="96"/>
+      <c r="E9" s="108" t="s">
         <v>125</v>
       </c>
-      <c r="F9" s="94"/>
+      <c r="F9" s="108"/>
       <c r="G9" s="23">
         <f>VLOOKUP(B8,'كل التخصصات'!A3:O87,13,1)</f>
         <v>0</v>
@@ -11647,15 +11647,15 @@
       <c r="I9" s="15"/>
     </row>
     <row r="10" spans="1:9" ht="26.25">
-      <c r="C10" s="93" t="str">
+      <c r="C10" s="96" t="str">
         <f>VLOOKUP(B8,'كل التخصصات'!A3:O87,6,1)</f>
         <v>//</v>
       </c>
-      <c r="D10" s="93"/>
-      <c r="E10" s="94" t="s">
+      <c r="D10" s="96"/>
+      <c r="E10" s="108" t="s">
         <v>126</v>
       </c>
-      <c r="F10" s="94"/>
+      <c r="F10" s="108"/>
       <c r="G10" s="23">
         <f>VLOOKUP(B8,'كل التخصصات'!A3:O87,14,1)</f>
         <v>0</v>
@@ -11668,10 +11668,10 @@
       <c r="B11" s="95"/>
       <c r="C11" s="95"/>
       <c r="D11" s="95"/>
-      <c r="E11" s="94" t="s">
+      <c r="E11" s="108" t="s">
         <v>127</v>
       </c>
-      <c r="F11" s="94"/>
+      <c r="F11" s="108"/>
       <c r="G11" s="23">
         <f>VLOOKUP(B8,'كل التخصصات'!A3:O87,15,1)</f>
         <v>0</v>
@@ -11682,65 +11682,65 @@
       <c r="B12" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C12" s="97" t="str">
+      <c r="C12" s="110" t="str">
         <f>VLOOKUP(B8,'كل التخصصات'!A3:O87,11,1)</f>
         <v>دراسات لغوية</v>
       </c>
-      <c r="D12" s="97"/>
-      <c r="E12" s="97"/>
+      <c r="D12" s="110"/>
+      <c r="E12" s="110"/>
     </row>
     <row r="13" spans="1:9" ht="26.25">
       <c r="A13" s="4"/>
       <c r="B13" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C13" s="98" t="str">
+      <c r="C13" s="111" t="str">
         <f>VLOOKUP(B8,'كل التخصصات'!A3:O87,12,1)</f>
         <v>تعليمية اللغات</v>
       </c>
-      <c r="D13" s="98"/>
-      <c r="E13" s="98"/>
+      <c r="D13" s="111"/>
+      <c r="E13" s="111"/>
     </row>
     <row r="14" spans="1:9" ht="27" customHeight="1">
       <c r="A14" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B14" s="99" t="str">
+      <c r="B14" s="112" t="str">
         <f>VLOOKUP(B8,'كل التخصصات'!A3:O87,2,1)</f>
         <v>محتوى النصوص و استراتيجية تحليلها و أثرها في تحقيق الكفاءة القاعدية _مستوى الطور المتوسط انموذجا_</v>
       </c>
-      <c r="C14" s="99"/>
-      <c r="D14" s="99"/>
-      <c r="E14" s="99"/>
-      <c r="F14" s="99"/>
-      <c r="G14" s="99"/>
-      <c r="H14" s="99"/>
+      <c r="C14" s="112"/>
+      <c r="D14" s="112"/>
+      <c r="E14" s="112"/>
+      <c r="F14" s="112"/>
+      <c r="G14" s="112"/>
+      <c r="H14" s="112"/>
     </row>
     <row r="15" spans="1:9" ht="33" thickBot="1">
-      <c r="B15" s="100" t="s">
+      <c r="B15" s="113" t="s">
         <v>28</v>
       </c>
-      <c r="C15" s="100"/>
-      <c r="D15" s="100"/>
-      <c r="E15" s="100"/>
-      <c r="F15" s="100"/>
-      <c r="G15" s="100"/>
+      <c r="C15" s="113"/>
+      <c r="D15" s="113"/>
+      <c r="E15" s="113"/>
+      <c r="F15" s="113"/>
+      <c r="G15" s="113"/>
     </row>
     <row r="16" spans="1:9" ht="26.25">
       <c r="A16" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B16" s="101" t="s">
+      <c r="B16" s="114" t="s">
         <v>30</v>
       </c>
-      <c r="C16" s="101"/>
+      <c r="C16" s="114"/>
       <c r="D16" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E16" s="101" t="s">
+      <c r="E16" s="114" t="s">
         <v>32</v>
       </c>
-      <c r="F16" s="101"/>
+      <c r="F16" s="114"/>
       <c r="G16" s="8" t="s">
         <v>33</v>
       </c>
@@ -11749,57 +11749,57 @@
       <c r="A17" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="B17" s="106" t="str">
+      <c r="B17" s="97" t="str">
         <f>VLOOKUP(B8,'كل التخصصات'!A3:O87,7,1)</f>
         <v>قاسم قادة</v>
       </c>
-      <c r="C17" s="106"/>
+      <c r="C17" s="97"/>
       <c r="D17" s="10" t="str">
         <f>VLOOKUP(B8,'كل التخصصات'!A3:O87,8,1)</f>
         <v>أستاذ التعليم العالي</v>
       </c>
-      <c r="E17" s="107" t="s">
+      <c r="E17" s="98" t="s">
         <v>35</v>
       </c>
-      <c r="F17" s="107"/>
+      <c r="F17" s="98"/>
       <c r="G17" s="11"/>
     </row>
     <row r="18" spans="1:7" ht="30">
       <c r="A18" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="B18" s="106" t="str">
+      <c r="B18" s="97" t="str">
         <f>VLOOKUP(B8,'كل التخصصات'!A3:O87,3,1)</f>
         <v>فارز فاطمة</v>
       </c>
-      <c r="C18" s="106"/>
+      <c r="C18" s="97"/>
       <c r="D18" s="10" t="str">
         <f>VLOOKUP(B8,'كل التخصصات'!A3:O87,4,1)</f>
         <v xml:space="preserve">استاذ التعليم العالي </v>
       </c>
-      <c r="E18" s="107" t="s">
+      <c r="E18" s="98" t="s">
         <v>35</v>
       </c>
-      <c r="F18" s="107"/>
+      <c r="F18" s="98"/>
       <c r="G18" s="11"/>
     </row>
     <row r="19" spans="1:7" ht="30.75" thickBot="1">
       <c r="A19" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="108" t="str">
+      <c r="B19" s="99" t="str">
         <f>VLOOKUP(B8,'كل التخصصات'!A3:O87,9,1)</f>
         <v xml:space="preserve">بالول أحمد </v>
       </c>
-      <c r="C19" s="108"/>
+      <c r="C19" s="99"/>
       <c r="D19" s="13" t="str">
         <f>VLOOKUP(B8,'كل التخصصات'!A3:O87,10,1)</f>
         <v>أستاذ التعليم العالي</v>
       </c>
-      <c r="E19" s="96" t="s">
+      <c r="E19" s="109" t="s">
         <v>35</v>
       </c>
-      <c r="F19" s="96"/>
+      <c r="F19" s="109"/>
       <c r="G19" s="14"/>
     </row>
     <row r="20" spans="1:7" ht="30">
@@ -11811,15 +11811,15 @@
       <c r="D20" s="95"/>
     </row>
     <row r="21" spans="1:7" ht="23.25" customHeight="1">
-      <c r="A21" s="93" t="s">
+      <c r="A21" s="96" t="s">
         <v>124</v>
       </c>
-      <c r="B21" s="93"/>
-      <c r="C21" s="93"/>
-      <c r="D21" s="93"/>
-      <c r="E21" s="93"/>
-      <c r="F21" s="93"/>
-      <c r="G21" s="93"/>
+      <c r="B21" s="96"/>
+      <c r="C21" s="96"/>
+      <c r="D21" s="96"/>
+      <c r="E21" s="96"/>
+      <c r="F21" s="96"/>
+      <c r="G21" s="96"/>
     </row>
     <row r="22" spans="1:7" ht="12" customHeight="1">
       <c r="B22" s="15"/>
@@ -11830,15 +11830,15 @@
       <c r="A23" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="B23" s="103" t="s">
+      <c r="B23" s="93" t="s">
         <v>40</v>
       </c>
-      <c r="C23" s="103"/>
+      <c r="C23" s="93"/>
       <c r="D23" s="16"/>
-      <c r="E23" s="103" t="s">
+      <c r="E23" s="93" t="s">
         <v>41</v>
       </c>
-      <c r="F23" s="103"/>
+      <c r="F23" s="93"/>
       <c r="G23" s="16"/>
     </row>
     <row r="24" spans="1:7" ht="11.25" customHeight="1">
@@ -11850,15 +11850,15 @@
       <c r="G24" s="17"/>
     </row>
     <row r="25" spans="1:7" ht="23.25">
-      <c r="B25" s="103" t="s">
+      <c r="B25" s="93" t="s">
         <v>42</v>
       </c>
-      <c r="C25" s="103"/>
+      <c r="C25" s="93"/>
       <c r="D25" s="16"/>
-      <c r="E25" s="103" t="s">
+      <c r="E25" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="F25" s="103"/>
+      <c r="F25" s="93"/>
       <c r="G25" s="16"/>
     </row>
     <row r="26" spans="1:7" ht="12" customHeight="1">
@@ -11870,10 +11870,10 @@
       <c r="G26" s="17"/>
     </row>
     <row r="27" spans="1:7" ht="23.25">
-      <c r="B27" s="103" t="s">
+      <c r="B27" s="93" t="s">
         <v>44</v>
       </c>
-      <c r="C27" s="103"/>
+      <c r="C27" s="93"/>
       <c r="D27" s="16"/>
       <c r="E27" s="17"/>
       <c r="F27" s="17"/>
@@ -11883,17 +11883,17 @@
       <c r="C28" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="D28" s="105">
+      <c r="D28" s="94">
         <f ca="1">TODAY()</f>
-        <v>46148</v>
-      </c>
-      <c r="E28" s="105"/>
+        <v>46149</v>
+      </c>
+      <c r="E28" s="94"/>
       <c r="F28" s="19" t="s">
         <v>46</v>
       </c>
       <c r="G28" s="20">
         <f ca="1">TODAY()</f>
-        <v>46148</v>
+        <v>46149</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="30">
@@ -11911,6 +11911,27 @@
     </row>
   </sheetData>
   <mergeCells count="37">
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="B14:H14"/>
+    <mergeCell ref="B15:G15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A5:C5"/>
     <mergeCell ref="B27:C27"/>
     <mergeCell ref="D28:E28"/>
     <mergeCell ref="A29:B29"/>
@@ -11927,27 +11948,6 @@
     <mergeCell ref="E18:F18"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="C6:F7"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A21:G21"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="B14:H14"/>
-    <mergeCell ref="B15:G15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="E16:F16"/>
   </mergeCells>
   <pageMargins left="0.196850393700787" right="0.196850393700787" top="0.196850393700787" bottom="0.196850393700787" header="0.31496062992126" footer="0.31496062992126"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
